--- a/data_extactor/batch_10_fa/trimmed/batch_0038_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0038_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | روانی ایده‌ها | اصالت و ابتکار | تجسم فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | اصالت | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | هنرمندان جلوه‌های ویژه و پویانماها | مدیران هنری | طراحان گرافیک | طراحان داخلی | عکاسان</t>
+          <t>هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | پویانماها و طراحان جلوه‌های ویژه | مدیران هنری | طراحان گرافیک | طراحان داخلی | عکاسان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>خلق آثار هنری اصیل در قالب رسانه‌ها و تخصص‌های هنری متفرقه | ایده‌پردازی، طراحی اولیه و ساخت نمونه‌های آزمایشی آثار هنری | انتخاب و آماده‌سازی مواد، ابزارها و تکنیک‌های متناسب با نوع اثر | اجرای اثر هنری نهایی با استفاده از روش‌های دستی یا ابزارهای دیجیتال | مذاکره و تبادل نظر با کارفرمایان، گالری‌داران و نمایندگان هنری درباره سفارش‌ها | برآورد مواد اولیه، زمان‌بندی و هزینه‌های اجرایی پروژه‌های سفارشی | عکاسی و مستندسازی آثار نهایی جهت درج در کارنما (پورتفولیو) و کاتالوگ‌ها | بازاریابی و فروش آثار از طریق برگزاری نمایشگاه‌ها، گالری‌ها و بسترهای آنلاین | نگهداری و سازماندهی فضای کارگاهی، تجهیزات و موجودی مواد اولیه | آماده‌سازی، قاب‌گیری، بسته‌بندی و ارسال آثار هنری به خریداران و نمایشگاه‌ها</t>
+          <t>خلق آثار هنری اصیل در رسانه‌ها و تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | تدوین ایده‌ها، طرح‌های اولیه و نمونه‌های آزمایشی آثار هنری. | انتخاب و آماده‌سازی مواد، ابزارها و فنون متناسب با رسانه هنری. | اجرای آثار نهایی با روش‌های دستی و دیجیتال. | رایزنی با کارفرمایان، نگارخانه‌ها و نمایندگان درباره سفارش‌ها و الزامات آن‌ها. | برآورد مواد، زمان و هزینه پروژه‌های سفارشی. | عکاسی و مستندسازی آثار تکمیل‌شده برای نمونه‌کارها و کاتالوگ‌ها. | بازاریابی و فروش آثار از راه نمایشگاه‌ها، نگارخانه‌ها و بسترهای برخط. | نگهداری فضای کارگاه، تجهیزات و موجودی مواد. | قاب‌بندی، نصب، بسته‌بندی و ارسال آثار هنری به مشتریان و محل‌های نمایش. | مطالعه تاریخ هنر، روندها و فنون برای پرورش شیوه هنری. | تهیه پیشنهادها و درخواست‌ها برای دریافت اعتبار، اقامت هنری و سفارش‌های عمومی. | برگزاری کارگاه آموزشی و نمایش عملی فنون برای هنرجویان و عموم مردم. | مرمت، حفاظت یا بازآفرینی آثار موجود در صورت دریافت سفارش.</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | اصالت و ابتکار | دید نزدیک | استدلال قیاسی | تجسم فضایی | درک شفاهی | درک کتبی</t>
+          <t>روانی ایده‌ها | اصالت | بینایی نزدیک | استدلال قیاسی | تجسم | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>طراحان مد و لباس | مهندسان صنایع | طراحان داخلی | مهندسان تولید | مهندسان مواد | نقشه‌کشان مکانیک | مهندسان مکانیک</t>
+          <t>طراحان مد و پوشاک | مهندسان صنایع | طراحان داخلی | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | نقشه‌کشان مکانیک | مهندسان مکانیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>بررسی و تعیین مشخصات ظاهری، کارکردی و ارگونومیک خطوط تولید محصول | هماهنگی و همفکری با واحدهای مهندسی، بازاریابی، تولید و فروش در خصوص مفاهیم طراحی | ارزیابی امکان‌پذیری طرح‌ها از نظر ایمنی، کارایی، هزینه‌های ساخت و بازخورد بازار | تهیه طرح‌های اولیه، نقشه‌های اجرایی دقیق و مستندات فنی با نرم‌افزارهای CAD | ساخت نمونه‌های اولیه (پروتوتایپ) با متریال‌های مختلف برای ارزیابی عملکردی | اصلاح و بازنگری طرح‌ها بر اساس آزمون‌های فنی، محدودیت‌های تولید و بازخورد مشتریان | ارائه طرح‌ها و گزارش‌های فنی به مدیران و کارفرمایان جهت اخذ تاییدیه نهایی | تحقیق در زمینه ویژگی‌های کیفی، استانداردهای ایمنی، مواد اولیه و روش‌های نوین تولید | تعیین مشخصات بسته‌بندی، گرافیک محصول و راهنماهای کاربری | نظارت بر روند ساخت نمونه‌ها و پیاده‌سازی طرح‌ها در خطوط تولید کارخانه‌ها</t>
+          <t>ارائه مشاوره به شرکت‌ها در موضوعات مربوط به پروژه‌ها یا مسائل هویت بصری سازمان. | رایزنی با واحدهای مهندسی، بازاریابی، تولید یا فروش، یا با مشتریان، برای تعیین و ارزیابی ایده‌های طراحی محصولات تولیدی. | هماهنگ‌سازی ظاهر و کارکرد خطوط محصول. | طراحی مواد گرافیکی برای استفاده به‌عنوان تزئین، تصویرسازی یا تبلیغات روی کالاهای تولیدی و بسته‌بندی یا ظروف. | تدوین استانداردهای صنعتی و دستورالعمل‌های نظارتی. | تدوین رویه‌های تولید و پایش ساخت طرح‌های خود در کارخانه برای بهبود عملیات و کیفیت محصول. | هدایت و هماهنگی ساخت مدل‌ها یا نمونه‌ها و تهیه نقشه‌های اجرایی و برگه‌های مشخصات از روی طرح‌های اولیه. | ارزیابی امکان‌پذیری ایده‌های طراحی، بر پایه عواملی مانند ظاهر، ایمنی، کارکرد، قابلیت تعمیر، بودجه، هزینه‌ها و روش‌های تولید، و ویژگی‌های بازار. | ساخت مدل یا نمونه از کاغذ، چوب، شیشه، پارچه، پلاستیک، فلز یا سایر مواد، با ابزارهای دستی یا برقی. | بررسی ویژگی‌های محصول مانند ایمنی و کیفیت جابه‌جایی آن، جذابیت بازاری، کارایی تولید، و شیوه‌های توزیع، استفاده و نگهداری آن. | اصلاح و پالایش طرح‌ها با استفاده از مدل‌های اجرایی، برای انطباق با مشخصات مشتری، محدودیت‌های تولید یا تغییر روندهای طراحی. | مشارکت در برنامه‌ریزی محصول جدید یا پژوهش بازار، از جمله بررسی نیاز بالقوه به محصولات جدید. | تهیه طرح‌های اولیه ایده‌ها، نقشه‌های تفصیلی، تصویرسازی، آثار هنری یا نقشه‌های اجرایی، با استفاده از ابزارهای نقشه‌کشی، رنگ و قلم‌مو یا تجهیزات طراحی به کمک رایانه. | ارائه طرح‌ها و گزارش‌ها به مشتریان یا کمیته‌های طراحی برای تأیید و گفت‌وگو درباره لزوم اصلاح. | مطالعه نشریات، حضور در نمایشگاه‌ها و بررسی محصولات رقیب و سبک‌ها و نقش‌مایه‌های طراحی برای کسب دید و پرورش ایده‌های طراحی. | پژوهش درباره مشخصات تولید، هزینه‌ها، مواد اولیه و روش‌های ساخت و ارائه برآورد هزینه و فهرست تفصیلی الزامات تولید. | سرپرستی کار دستیاران در سراسر فرایند طراحی.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>اصالت و ابتکار | درک کتبی | بیان شفاهی | روانی ایده‌ها | تجسم فضایی | دید نزدیک | تشخیص رنگ دیداری</t>
+          <t>اصالت | درک کتبی | بیان شفاهی | روانی ایده‌ها | تجسم | بینایی نزدیک | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوپردازان پارچه و پوشاک | طراحان گرافیک | دوزندگان دستی | متصدیان چرخ‌های خیاطی | خیاطان زنانه، مردانه و سفارشی‌دوز</t>
+          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | طراحان گرافیک | دوزندگان دستی | چرخکاران صنعتی | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>رصد و تحلیل روندهای جهانی مد، رنگ و پارچه از طریق نشریات و رویدادهای تخصصی | ترسیم طرح‌های اولیه و دستی البسه و اکسسوری به همراه جزئیات فنی و پالت رنگی | انتخاب انواع پارچه، تریم‌ها، یراق‌آلات و تعیین تکنیک‌های دوخت و تولید البسه | طراحی الگوهای پایه، برش قطعات و دوخت نمونه‌های اولیه جهت پرو و آزمون | بررسی، اصلاح و برازش نمونه‌های دوخته‌شده بر روی تن‌پوش یا مانکن | طراحی مجموعه‌های پوشاک سفارشی برای مشتریان خاص، تئاتر، تلویزیون یا سینما | همکاری و هماهنگی با خیاطان، الگوسازان و تکنسین‌های خط تولید در فرآیند دوخت | تعیین بازار هدف و قیمت‌گذاری محصولات متناسب با بودجه و بخش‌بندی بازار | آماده‌سازی شناسنامه فنی محصول و مشخصات مراقبت از پارچه جهت تولید انبوه | تهیه نمونه‌های نمایشی برای ارائه به مدیران فروش، کارفرمایان و رویدادهای معرفی محصول</t>
+          <t>تطبیق ایده‌های سایر طراحان برای بازار انبوه. | حضور در نمایش‌های مد و بررسی مجلات و راهنماهای پوشاک برای گردآوری اطلاعات درباره روندهای مد و ترجیحات مصرف‌کننده. | همکاری با سایر طراحان برای هماهنگی محصولات و طرح‌های ویژه. | رایزنی با مدیران فروش و مدیریت یا با مشتریان برای گفت‌وگو درباره ایده‌های طراحی. | طراحی پوشاک و لوازم جانبی سفارشی برای اشخاص، خرده‌فروشان یا تولیدات تئاتری، تلویزیونی یا سینمایی. | تعیین قیمت برای هر مدل. | تدوین مجموعه‌ای از محصولات یا لوازم جانبی و بازاریابی آن‌ها از راه بسترهایی مانند بوتیک‌ها یا کاتالوگ‌های سفارش پستی. | هدایت و هماهنگی کارکنانی که الگو می‌کشند و برش می‌دهند و نمونه یا پوشاک نهایی را می‌دوزند. | کشیدن الگو برای اقلام طراحی‌شده، برش الگو و برش پارچه مطابق الگو، با استفاده از ابزارهای اندازه‌گیری و قیچی. | بررسی نمونه لباس‌ها روی مدل و بیرون از آن و اصلاح طرح‌ها برای دستیابی به اثر دلخواه. | شناسایی بازارهای هدف طرح‌ها، با در نظر گرفتن عواملی مانند سن، جنسیت و جایگاه اجتماعی‌اقتصادی. | ارائه نمونه لباس به نمایندگان و کارشناسان فروش و ترتیب دادن نمایش نمونه‌ها در جلسات فروش یا نمایش‌های مد. | خرید اقلام پوشاک و لوازم جانبی نو یا دست‌دوم در صورت نیاز برای تکمیل طرح‌ها. | مطالعه فیلم‌نامه و رایزنی با کارگردانان و سایر عوامل تولید برای تدوین ایده‌های طراحی و برنامه‌ریزی تولید. | پژوهش درباره سبک‌ها و دوره‌های تاریخی پوشاک مورد نیاز تولیدات سینمایی یا تئاتری. | انتخاب مواد و فنون تولید مورد استفاده برای محصولات. | دوخت بخش‌های پارچه به یکدیگر برای ساخت ماکت یا نمونه لباس و اقلام، با استفاده از تجهیزات دوخت. | ترسیم طرح‌های اولیه و تفصیلی پوشاک یا لوازم جانبی و نگارش مشخصاتی مانند ترکیب رنگ، شیوه دوخت، نوع پارچه و الزامات لوازم جانبی. | آزمون پارچه‌ها یا نظارت بر آزمون آن‌ها تا برچسب راهنمای نگهداری لباس تهیه شود. | بازدید از نمایشگاه‌های پارچه برای به‌روز ماندن از جدیدترین منسوجات.</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری | فروش و بازاریابی | طراحی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | فروش و بازاریابی | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تجسم فضایی | دید نزدیک | تشخیص رنگ دیداری | اصالت و ابتکار | چابکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | تشخیص رنگ بصری | اصالت | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | طراحان مد و لباس | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | بسته‌بندها و کارگران بسته‌بندی دستی | فروشندگان خرده‌فروشی | انبارداران و متصدیان چیدمان و تحویل کالا</t>
+          <t>هنرمندان صنایع دستی | طراحان مد و پوشاک | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | کارگران بسته‌بندی دستی | فروشندگان خرده‌فروشی | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>بررسی و دریافت نیازها، ترجیحات، بودجه و زمان‌بندی مشتریان برای انواع سفارش‌ها | طراحی و چیدمان انواع دسته‌گل، سبد گل، پایه‌گل، تاج‌گل و تراریوم | انتخاب گل‌ها، شاخ‌وبرگ‌ها و تزئینات متناسب با فرم، رنگ و ماندگاری طرح | آماده‌سازی، هرس، تغذیه و نگهداری اصولی گل‌ها و گیاهان تازه در انبار و نمایشگاه | گل‌آرایی و اجرای دکوراسیون مجالس، تالارها، جشن‌ها، همایش‌ها و مراسم تشریفاتی | سفارش و خرید گل‌های شاخه‌بریده و اقلام مصرفی از عمده‌فروشان و تولیدکنندگان | بسته‌بندی، تزئین نهایی و قیمت‌گذاری بر روی محصولات آماده تحویل | ارائه مشاوره و راهنمایی به مشتریان در خصوص اصول نگهداری و ماندگاری گیاهان و گل‌ها | چیدمان، دیزاین و به‌روزرسانی ویترین و فضای فروشگاه جهت جذب مشتریان | مدیریت فرآیندهای مالی، صدور فاکتور و پیگیری ارسال دقیق سفارش‌ها به مقصد</t>
+          <t>برگزاری کلاس یا نمایش عملی، یا آموزش سایر کارکنان. | رایزنی با مشتریان درباره قیمت و نوع آرایش گل مورد نظر و تاریخ، زمان و محل تحویل. | ایجاد و تغییر ویترین و چیدمان داخلی فروشگاه، طرح‌ها و ظاهر آن برای ارتقای تصویر مغازه. | تزئین ساختمان‌ها، سالن‌ها، اماکن مذهبی یا سایر مکان‌ها برای مهمانی، مراسم ازدواج و سایر مناسبت‌ها، یا سرپرستی این تزئینات. | تحویل آرایش‌های گل به مشتریان، یا نظارت بر کارکنان مسئول تحویل. | آگاه‌سازی مشتریان درباره مراقبت، نگهداری و جابه‌جایی گل‌ها و شاخ‌وبرگ‌های گوناگون، گیاهان آپارتمانی و سایر اقلام. | سفارش و خرید گل و ملزومات از عمده‌فروشان و پرورش‌دهندگان. | انجام امور عمومی نظافت فروشگاه برای اطمینان از تمیزی و مرتب بودن مغازه. | انجام وظایف اداری و خدمات خرده‌فروشی، مانند نگهداری سوابق مالی، خدمت به مشتریان، پاسخ‌گویی تلفنی، فروش اقلام هدیه و دریافت وجه. | طراحی آرایش گل مطابق خواسته مشتری، با به‌کارگیری دانش طراحی و ویژگی‌های مواد، یا انتخاب الگوی طراحی استاندارد مناسب. | انتخاب گل و شاخ‌وبرگ برای آرایش‌ها، با کار روی ترکیب‌های متعدد برای ساخت و پرورش خلاقیت‌های تازه. | پیرایش مواد و آماده‌سازی دسته‌گل، تاج گل، تراریوم و سایر اقلام، با استفاده از قیچی، قالب، مفتول، سنجاق، چسب گل، فوم و سایر مواد. | بازکردن بسته‌های کالا هنگام ورود به مغازه. | آبیاری گیاهان و برش، آماده‌سازی و تمیز کردن گل و شاخ‌وبرگ برای نگهداری. | بسته‌بندی و قیمت‌گذاری آرایش‌های آماده‌شده.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>اصالت و ابتکار | روانی ایده‌ها | دید نزدیک | درک کتبی | درک شفاهی | بیان شفاهی | تشخیص رنگ دیداری</t>
+          <t>اصالت | روانی ایده‌ها | بینایی نزدیک | درک کتبی | درک شفاهی | بیان شفاهی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران هنری | صفحه‌آراها و ناشران رومیزی | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان دکوراسیون و ویترین مغازه | تکنسین‌ها و کارگران مراحل پیش از چاپ | هنرمندان جلوه‌های ویژه و پویانماها | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>مدیران هنری | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان دکوراسیون و ویترین مغازه | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | پویانماها و طراحان جلوه‌های ویژه | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>برگزاری جلسات مشاوره با کارفرمایان و مدیران جهت دریافت بریف و اهداف طراحی | خلق ایده‌ها، طرح‌های مفهومی، اتودهای اولیه و لی‌اوت‌های گرافیکی | انتخاب و هماهنگ‌سازی پالت‌های رنگی، ساختار تایپوگرافی، فونت‌ها و تصاویر | طراحی اقلام گرافیکی نظیر نشان‌واره (لوگو)، هویت بصری برند، بسته‌بندی و پوسترها | آماده‌سازی، بهینه‌سازی و خروجی‌گرفتن از فایل‌های دیجیتال نهایی برای چاپ و نشر دیجیتال | طراحی صفحات، بنرها و گرافیک‌های اختصاصی برای وب‌سایت‌ها و شبکه‌های اجتماعی | نظارت فنی بر فرآیند چاپ و تطابق کیفیت رنگی و ساختاری خروجی با استانداردهای طراحی | مدیریت و سازماندهی آرشیو فایل‌ها، دارایی‌های بصری، تایپ‌فیس‌ها و تصاویر | تعامل و هماهنگی با تیم‌های بازاریابی، تولید محتوا و چاپخانه‌ها | بازنگری و اعمال اصلاحات روی طرح‌ها بر اساس بازخورد مدیران هنری و سفارش‌دهندگان</t>
+          <t>رایزنی با مشتریان برای گفت‌وگو و تعیین طراحی چیدمان. | خلق طرح‌ها، ایده‌ها و نمونه چیدمان‌ها، بر پایه دانش اصول صفحه‌آرایی و مفاهیم زیبایی‌شناختی طراحی. | تعیین اندازه و آرایش مواد تصویری و متن، و انتخاب سبک و اندازه قلم. | تدوین گرافیک و چیدمان برای تصویرسازی محصول، نشان‌های شرکتی و وب‌سایت‌ها. | ترسیم و چاپ چارت‌ها، نمودارها، تصویرسازی‌ها و سایر آثار گرافیکی، با استفاده از رایانه. | وارد کردن اطلاعات در تجهیزات رایانه‌ای برای ساخت چیدمان برای مشتری یا سرپرست. | نگهداری بایگانی تصاویر، عکس‌ها یا آثار پیشین. | علامت‌گذاری، چسباندن و مونتاژ چیدمان‌های نهایی برای آماده‌سازی جهت چاپ. | عکاسی از چیدمان‌ها با دوربین برای تهیه نسخه چاپی چیدمان جهت ارائه به سرپرستان یا مشتریان. | آماده‌سازی فایل‌های دیجیتال برای چاپ. | تهیه تصویرسازی یا طرح‌های اولیه مواد، گفت‌وگو درباره آن‌ها با مشتریان یا سرپرستان و اعمال تغییرات لازم. | تهیه یادداشت‌ها و دستورالعمل برای کارکنانی که چیدمان‌های نهایی را برای چاپ مونتاژ و آماده می‌کنند. | تولید گرافیک ثابت و متحرک برای بخش‌های زنده و ضبط‌شده اخبار تلویزیونی، با استفاده از تجهیزات ویدئویی الکترونیکی. | پژوهش درباره نرم‌افزارها یا مفاهیم طراحی جدید. | پژوهش درباره مخاطب هدف پروژه‌ها. | بازبینی چیدمان‌های نهایی و ارائه پیشنهاد برای بهبود، در صورت نیاز. | مطالعه تصویرسازی‌ها و عکس‌ها برای برنامه‌ریزی نحوه ارائه مواد، محصولات یا خدمات. | استفاده از نرم‌افزارهای رایانه‌ای برای تولید تصاویر جدید. | نگارش یا ویرایش متن برای مشتریان.</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>طراحی | خدمات مشتریان و خدمات فردی | ساختمان و ساخت‌وساز | فروش و بازاریابی | رایانه و الکترونیک | هنرهای زیبا</t>
+          <t>طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | فروش و بازاریابی | رایانه و الکترونیک | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | اصالت و ابتکار | درک شفاهی | بیان شفاهی | تجسم فضایی | دید نزدیک | تشخیص رنگ دیداری</t>
+          <t>روانی ایده‌ها | اصالت | درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | نجاران | نصابان موکت و کف‌پوش | طراحان گرافیک | طراحان دکوراسیون و ویترین مغازه | طراحان صحنه و نمایشگاه</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | نجاران و درودگران | موکت‌کاران و نصابان فرش | طراحان گرافیک | طراحان دکوراسیون و ویترین مغازه | طراحان صحنه و نمایشگاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>مشاوره با کارفرمایان جهت شناسایی نیازها، کاربری فضا، سبک مورد نظر و تعیین بودجه | طراحی پلان‌های چیدمان، نقشه‌های اجرایی، سقف کاذب، نورپردازی و تاسیسات داخلی | تهیه مدل‌های سه‌بعدی و رندرهای واقع‌گرایانه با نرم‌افزارهای تخصصی CAD و 3D | انتخاب و پیشنهاد متریال‌ها، پوشش‌های کف و دیوار، مبلمان، روشنایی و اکسسوری‌ها | برآورد مقادیر متریال، تهیه صورت مقادیر و برآورد هزینه‌های اجرایی پروژه | هماهنگی مستمر با معماران، مهندسان تاسیسات، پیمانکاران و مجریان ساختمانی | نظارت میدانی و مستمر بر عملیات اجرایی و تطابق آن با نقشه‌ها و جزئیات طراحی | رعایت ضوابط فنی، مقررات ملی ساختمان، استانداردهای دسترس‌پذیری و ایمنی آتش‌نشانی | تهیه نقشه‌های جزئیات اجرایی (Shop Drawings) برای عناصر سفارشی مانند کابینت و کمدها | مدیریت خرید، تدارکات و نصب نهایی المان‌های دکوراتیو و تجهیزات داخلی</t>
+          <t>ارائه مشاوره به کارفرما درباره عوامل طراحی داخلی، مانند برنامه‌ریزی فضا، چیدمان و استفاده از مبلمان یا تجهیزات، و هماهنگی رنگ. | رایزنی با کارفرما برای تعیین عوامل مؤثر بر برنامه‌ریزی فضاهای داخلی، مانند بودجه، ترجیحات معماری، هدف و کارکرد. | هماهنگی با سایر متخصصان، مانند پیمانکاران، معماران، مهندسان و لوله‌کش‌ها، برای تضمین موفقیت کار. | طراحی نقشه‌ها به‌گونه‌ای که ایمن و منطبق بر الزامات دسترس‌پذیری معلولان (ADA) باشد. | طراحی فضاها به‌شکل سازگار با محیط‌زیست، با استفاده از مواد پایدار و بازیافتی در صورت امکان. | برآورد نیازها و هزینه‌های مواد و ارائه طرح به کارفرما برای تأیید. | تدوین طرح فضا به‌گونه‌ای که کاربردی، زیبا و متناسب با اهداف مورد نظر باشد، مانند افزایش بهره‌وری یا فروش کالا. | بازرسی کار ساخت در محل برای اطمینان از رعایت نقشه‌های طراحی. | برنامه‌ریزی و طراحی فضاهای داخلی قایق، هواپیما، اتوبوس، قطار و سایر فضاهای بسته. | ارائه ایده‌های طراحی در قالب کلاژ یا نقشه. | پژوهش و کاوش درباره استفاده از مواد، فناوری‌ها و محصولات جدید برای به‌کارگیری در طرح‌ها. | پژوهش درباره الزامات آیین‌نامه‌های بهداشت و ایمنی برای پشتیبانی از طراحی. | بازبینی و تهیه جزئیات نقشه‌های کارگاهی برای طرح‌های ساخت. | انتخاب یا طراحی و خرید مبلمان، آثار هنری و لوازم جانبی. | واگذاری ساخت، نصب و چیدمان موکت، تجهیزات ثابت، لوازم جانبی، پرده، رنگ و پوشش دیوار، آثار هنری، مبلمان و اقلام مرتبط به پیمانکاران فرعی. | استفاده از نقشه‌کشی به کمک رایانه (CAD) و نرم‌افزارهای مرتبط برای تولید اسناد اجرایی.</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>تجسم فضایی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | چابکی دستی | دید نزدیک | تشخیص رنگ دیداری</t>
+          <t>تجسم | درک شفاهی | بیان شفاهی | روانی ایده‌ها | مهارت دستی | بینایی نزدیک | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | نمایش‌دهندگان و مروجان کالا | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان گرافیک | طراحان داخلی | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه</t>
+          <t>طراحان تجاری و صنعتی | معرفی‌کنندگان و مروجان کالا | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان گرافیک | طراحان داخلی | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ایده‌پردازی و طراحی کانسپت‌های بصری برای ویترین و دکورهای داخل فروشگاه | مونتاژ، نصب و آرایش المان‌های دکوراتیو، استندها، بک‌دراپ‌ها و سازه‌های نمایشی | پوشاندن، استایل‌دهی و چیدمان مانکن‌ها متناسب با سبک و روندهای فصل | چیدمان هدفمند و جذاب محصولات در قفسه‌ها، ویترین‌ها و فضاهای تبلیغاتی | تنظیم زوایای نورپردازی، پالت‌های رنگی و نورهای نقطه‌ای روی کالاها | طراحی، ساخت و نصب تابلوهای راهنما، برچسب‌های قیمت و پوسترهای پروموشن | تغییر دوره‌ای و بازچیدمان دکوراسیون متناسب با کمپین‌های تبلیغاتی و فصول | نگهداری، ترمیم و انبارداری وسایل تزئینی، مانکن‌ها و تجهیزات دکور | تعامل مستمر با مدیران فروشگاه و بازاریابی در خصوص معرفی محصولات کلیدی | آموزش کارکنان فروش در خصوص حفظ نظم چیدمان و هماهنگی رنگی البسه و کالاها</t>
+          <t>چیدمان لوازم صحنه، مبلمان، کالا، پس‌زمینه یا سایر لوازم جانبی، مطابق طرح‌های اولیه آماده‌شده. | مونتاژ یا برپایی ویترین، مبلمان یا محصولات در فضای فروشگاه، با استفاده از رنگ، نور، تصویر یا سایر لوازم جانبی برای نمایش محصول. | شرکت در دوره‌های آموزشی یا جلسات برنامه‌ریزی شرکت برای دریافت ایده‌های تازه جهت معرفی محصولات. | تغییر یا جابه‌جایی ویترین‌ها، فضاهای نمایش داخلی یا تابلوها متناسب با تغییر موجودی یا برنامه‌های ترویجی. | همکاری با دیگران برای تأمین محصولات یا سایر اقلام نمایشی. | ساخت یا مونتاژ ویترین‌ها یا اجزای آن‌ها از پارچه، شیشه، کاغذ یا پلاستیک، با ابزارهای دستی یا ابزارهای برقی نجاری، مطابق مشخصات. | رایزنی با کارکنان تبلیغات یا فروش برای تعیین نوع کالای برجسته‌شده و زمان و مکان هر ویترین. | رایزنی با مدیران فروشگاه، خریداران، همکاران فروش، کارکنان خدمات یا کارکنان فنی برای تعیین محل مناسب ویترین‌ها یا محصولات. | برش طرح‌ها روی مقوا، تخته فشرده یا تخته‌سه‌لایی، مطابق نقش‌مایه رویداد. | تدوین ایده‌ها یا طرح‌های ویترین کالا یا تزئین ویترین. | پوشاندن لباس بر مانکن‌ها برای ویترین. | نصب غرفه، نمایشگاه، ویترین، موکت یا پرده، مطابق نقشه طبقات ساختمان یا مشخصات. | نصب تزئینات، مانند پرچم، بنر، چراغ‌های تزئینی یا پارچه‌آرایی روی ساختمان، خیابان، سالن نمایشگاه یا غرفه یا در داخل آن‌ها. | آموزش کارکنان فروش در زمینه هماهنگی رنگ رگال‌های پوشاک یا ویترین‌های پیشخوان. | نگهداری لوازم صحنه، محصولات یا مانکن‌ها، بازرسی آن‌ها از نظر عیب، ترمیم جزئی، نظافت پس از مراجعه مشتریان یا اعمال پوشش‌های محافظ در صورت نیاز. | دریافت نقشه‌ها از طراحان یا مدیران ویترین و گفت‌وگو درباره اجرای آن‌ها با مشتریان یا سرپرستان. | قرار دادن برچسب قیمت یا تابلوهای توضیحی روی پس‌زمینه، تجهیزات ثابت، کالا یا کف. | طراحی ویترین‌های تجاری برای جلب و جذب مشتریان. | تهیه طرح‌های اولیه، نقشه‌های طبقات یا ماکت ویترین‌های پیشنهادی. | انتخاب درون‌مایه، نورپردازی، رنگ یا لوازم صحنه مورد استفاده. | نگهداری، بسته‌بندی و ثبت سوابق موجودی لوازم صحنه، محصولات یا اقلام نمایشی. | سرپرستی یا آموزش کارکنان در وظایف روزانه، مانند چیدمان بصری کالا. | عکاسی از ویترین‌ها یا تابلوها. | استفاده از رایانه برای تولید تابلو و علائم.</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | درک شفاهی | تجسم فضایی | درک کتبی | اصالت و ابتکار | حساسیت به مسئله | دید نزدیک</t>
+          <t>روانی ایده‌ها | درک شفاهی | تجسم | درک کتبی | اصالت | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماران منظر و سازه‌های دریایی | مدیران هنری | متصدیان لباس صحنه | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | کارشناسان فنی و مرمت‌کاران موزه</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدیران هنری | متصدیان و جامه داران لباس صحنه | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | تکنسین‌ها و مرمت‌گران موزه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>مطالعه دقیق فیلم‌نامه، نمایشنامه یا اهداف نمایشگاه جهت تدوین کانسپت صحنه | تحقیق در خصوص ویژگی‌های معماری، اقلیمی و سبک‌های تاریخی دوره مورد نظر | تهیه اسکیس‌های مفهومی، نقشه‌های اجرایی، پلان‌های چیدمان و ماکت‌های مقیاسی | برگزاری جلسات هماهنگی با کارگردان، طراح نور، صدابردار و مدیر تولید | برآورد هزینه‌ها، انتخاب متریال‌های سازه‌ای و تدوین بودجه ساخت دکور و غرفه‌ها | نظارت مستقیم بر عملیات ساخت، نصب، رنگ‌آمیزی و ایمنی سازه‌های صحنه | انتخاب و تهیه وسایل صحنه (آکسسوار)، مبلمان، پرده‌ها و جزئیات دکوراتیو | حضور در جلسات تمرین جهت ارزیابی کارایی صحنه با زوایای دوربین و حرکت بازیگران | طراحی و تعبیه تدابیر ایمنی، مسیرهای تردد و ضوابط حفاظتی در غرفه‌ها و صحنه‌ها | هماهنگی برای جمع‌آوری، تفکیک و انبارداری سازه‌ها و وسایل صحنه پس از پایان پروژه</t>
+          <t>تهیه نمونه‌ها یا آثار گرافیکی مورد نیاز برای تکمیل نمایشگاه، یا ترتیب دادن تهیه آن‌ها. | ترتیب دادن قرارداد با پیمانکاران بیرونی برای ساخت سازه‌های نمایشگاهی. | واگذاری وظایف به کارکنان برای تکمیل ایده‌های طراحی و تهیه طرح‌های اولیه، تصویرسازی و نقشه‌های تفصیلی صحنه، یا گرافیک و پویانمایی. | حضور در تمرین‌ها و جلسات تولید برای دریافت و انتقال اطلاعات مرتبط با صحنه. | همکاری با مسئولان نور و صدا تا این جنبه‌های تولید با طراحی صحنه یا چیدمان نمایشگاه هماهنگ شود. | رایزنی با کارفرمایان و کارکنان برای گردآوری اطلاعات درباره فضای نمایشگاه، درون‌مایه و محتوای پیشنهادی، زمان‌بندی، بودجه، مواد یا الزامات تبلیغاتی. | رایزنی با مرمتگران برای تعیین شیوه مدیریت جنبه‌های محیطی نمایشگاه، مانند نور، دما و رطوبت، تا اشیا محافظت شوند و نمایشگاه ارتقا یابد. | هماهنگی برچیدن صحنه‌ها، لوازم صحنه و نمایشگاه‌ها پس از پایان تولید یا رویداد. | هماهنگی حمل صحنه‌هایی که خارج از محل ساخته شده‌اند و هماهنگی برپایی آن‌ها در محل استفاده. | طراحی و ساخت ماکت مقیاس‌دار طرح‌های صحنه، یا صحنه‌های کوچک‌مقیاس مورد استفاده در فیلم‌برداری پس‌زمینه یا جلوه‌های ویژه. | طراحی و تولید ویترین‌ها و موادی که برای تزئین ویترین، چیدمان داخلی یا محل برگزاری رویداد، مانند خیابان‌ها و محوطه‌های نمایشگاهی، به کار می‌روند. | تدوین طرح‌های صحنه، بر پایه ارزیابی فیلم‌نامه، بودجه، اطلاعات پژوهشی و لوکیشن‌های در دسترس. | هدایت و هماهنگی فعالیت‌های ساخت، برپایی یا تزئین برای اطمینان از انطباق صحنه‌ها یا نمایشگاه‌ها با الزامات طراحی، بودجه و زمان‌بندی. | برآورد هزینه‌های مرتبط با صحنه یا نمایشگاه، شامل مواد، ساخت و اجاره لوازم صحنه یا لوکیشن. | بررسی اشیایی که قرار است در نمایشگاه قرار گیرند برای برنامه‌ریزی محل و شیوه نمایش آن‌ها. | گنجاندن سامانه‌های امنیتی در چیدمان نمایشگاه. | بازرسی نمایشگاه‌های برپاشده از نظر انطباق با مشخصات و عملکرد رضایت‌بخش اجزای جلوه‌های ویژه. | مشاهده صحنه‌ها در حین تمرین برای اطمینان از اینکه عناصر صحنه با جنبه‌های اجرایی مانند حرکت بازیگران و زوایای دوربین تداخل ندارند. | برنامه‌ریزی برای مسائل خاص هر مکان، مانند محدودیت فضا، الگوهای رفت‌وآمد و ملاحظات ایمنی. | تهیه پرداخت‌های اولیه نمایشگاه‌های پیشنهادی، شامل مشخصات تفصیلی ساخت، چیدمان و مواد، و نمودارهای مرتبط با جنبه‌هایی مانند جلوه‌های ویژه یا نورپردازی. | تهیه پیش‌نویس‌های اولیه و نقشه‌های اجرایی مقیاس‌دار صحنه، شامل نقشه طبقات، دکور و لوازم صحنه‌ای که باید ساخته شوند. | تهیه مواد پشتیبان برای نمایشگاه‌ها و ویترین‌ها، مانند بسته‌های خبری، تبلیغات، اطلاعیه‌های رسانه‌ای، پوستر، بروشور، کاتالوگ و کارت دعوت. | مطالعه فیلم‌نامه برای تعیین الزامات لوکیشن، صحنه و طراحی. | پژوهش درباره عناصر معماری و سبکی متناسب با دوره تاریخی مورد نظر، و رایزنی با کارشناسان برای کسب اطلاعات در صورت لزوم. | انتخاب و خرید چوب و یراق‌آلات لازم برای ساخت صحنه. | انتخاب لوازم صحنه، مانند مبلمان، تابلو، چراغ و فرش. | ارائه نقشه‌ها برای تأیید و تطبیق آن‌ها با اهداف مورد نظر یا با محدودیت‌های بودجه‌ای و ساخت.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | روانی ایده‌ها | اصالت و ابتکار | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | روانی ایده‌ها | اصالت | تجسم</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | طراحان گرافیک | طراحان داخلی | طراحان مد و لباس | طراحان صحنه و نمایشگاه | طراحان دکوراسیون و ویترین مغازه | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>طراحان تجاری و صنعتی | طراحان گرافیک | طراحان داخلی | طراحان مد و پوشاک | طراحان صحنه و نمایشگاه | طراحان دکوراسیون و ویترین مغازه | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>طراحی محصولات، فضاها و اقلام بصری در حوزه‌های تخصصی و طبقه‌بندی‌نشده | مشاوره با کارفرمایان جهت تعیین الزامات طراحی، زمان‌بندی و بودجه اجرایی | تحقیق در زمینه متریال‌ها، فناوری‌های نوین، نیازهای کاربر و روندهای بازار | تهیه طرح‌های اولیه دستی، نقشه‌های فنی دقیق و مدل‌های دیجیتال سه‌بعدی | انتخاب رنگ‌ها، متریال‌ها، پرداخت‌های سطحی و قطعات متناسب با طرح | ساخت مدل‌های اولیه و ماکت‌های آزمایشی برای ارزیابی عملکرد و ارگونومی | ارائه پروپوزال‌ها و طرح‌ها به کارفرما و اصلاح آن‌ها بر اساس بازخوردها | هماهنگی و نظارت بر سازندگان، تامین‌کنندگان و تولیدکنندگان در طول فرآیند ساخت | تهیه مستندات فنی، مشخصات اجرایی و برآورد هزینه‌های تولید | انطباق طرح‌ها با استانداردهای کیفی، ضوابط ایمنی و مقررات زیست‌محیطی</t>
+          <t>طراحی محصولات، فضاها و ویترین‌ها در تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | رایزنی با کارفرمایان برای تعیین الزامات طراحی، بودجه و زمان‌بندی. | پژوهش درباره مواد، روش‌ها، روندهای بازار و نیازهای کاربر. | تهیه طرح‌های اولیه ایده، پرداخت‌ها، ماکت‌ها و نقشه‌های فنی. | انتخاب رنگ، مواد، پرداخت‌ها و اجزای طرح. | ساخت نمونه اولیه و ماکت برای ارزیابی ظاهر و کارکرد. | ارائه پیشنهادهای طراحی به کارفرمایان و بازنگری آن‌ها بر پایه بازخورد. | هماهنگی با سازندگان، کارگاه‌ها و تأمین‌کنندگان در جریان تولید. | تهیه مشخصات، برآورد هزینه و مستندات تولید. | بازرسی کار تکمیل‌شده برای راستی‌آزمایی انطباق با هدف طراحی و استانداردهای کیفیت. | حصول اطمینان از انطباق طرح‌ها با الزامات ایمنی، دسترس‌پذیری و مقررات. | نگهداری پرونده‌های طراحی، نمونه مواد و سوابق تأمین‌کنندگان. | پیگیری زمان‌بندی و بودجه پروژه تا تکمیل آن. | تهیه نمونه‌کار و مواد تبلیغاتی برای جذب مشتری.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | زبان انگلیسی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی</t>
+          <t>هنرهای زیبا | زبان انگلیسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حفظ کردن | وضوح گفتار | اصالت و ابتکار | روانی ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حفظ کردن | وضوح گفتار | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارگزاران و مدیران برنامه‌های هنرمندان، مجریان و ورزشکاران | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | گویندگان پخش و مجریان رادیویی | رقصندگان | چهره‌پردازان تئاتر و سینما | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان</t>
+          <t>مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | گویندگان پخش و مجریان رادیویی | هنرمندان رقص و حرکات موزون | چهره‌پردازان و گریموران تئاتر و سینما | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>شرکت در آزمون‌های انتخاب بازیگر (کستینگ) و تست‌های بازیگری | مطالعه و تحلیل عمیق فیلم‌نامه و نمایشنامه برای شناخت ابعاد شخصیتی نقش | تمرین، یادگیری و از بر کردن دیالوگ‌ها، نشانه‌ها و میزانسن‌های تعیین‌شده | همکاری نزدیک با کارگردان، نویسنده و سایر بازیگران جهت رسیدن به لحن مناسب | اجرای نقش با به‌کارگیری تکنیک‌های بیانی، لحن، حالات چهره و حرکات بدنی | هماهنگی کامل با سایر عوامل صحنه از جمله گریمور، طراح لباس، صدابردار و نورپرداز | حضور منظم و متعهدانه در جلسات دورخوانی، تمرین‌های صحنه و ضبط نهایی | گویندگی، روایتگری یا صداپیشگی برای انیمیشن‌ها، فیلم‌ها و نمایش‌های رادیویی | فراگیری و اجرای حرکات مهارتی، تکنیک‌های بدنی یا بدلکاری‌های سبک تحت نظارت مربی | شرکت در نشست‌های خبری، مصاحبه‌ها و رویدادهای ترویجی جهت معرفی اثر</t>
+          <t>شرکت در آزمون بازیگری و فراخوان انتخاب بازیگر برای دریافت نقش. | همکاری با سایر بازیگران به‌عنوان بخشی از یک گروه اجرایی. | ساخت عروسک و آدمک شکم‌گویی و دوخت لباس‌های جانبی، با ابزارهای دستی و ماشین. | پوشیدن لباس و گریم دلقک و اجرای برنامه‌های کمدی برای سرگرمی تماشاگران. | معرفی اجراها و اجراکنندگان برای برانگیختن شور و هماهنگی گذار روان میان بخش‌های برنامه در رویدادها. | شناخت شخصیت‌های فیلم‌نامه و روابط آنان با یکدیگر برای پرورش برداشت از نقش. | اجرای برداشت‌های طنزآمیز و جدی از احساسات، کنش‌ها و موقعیت‌ها، با استفاده از حرکات بدن، حالات چهره و اشاره. | اجرای شعبده‌های اصیل و متداول برای سرگرم و شگفت‌زده کردن تماشاگران، گاه با مشارکت دادن خود آنان. | ایفا و تفسیر نقش، با استفاده از گفتار، اشاره و حرکات بدن، برای سرگرمی، آگاهی‌بخشی یا آموزش مخاطبان رادیو، سینما، تلویزیون یا اجرای زنده. | آماده‌سازی و اجرای بدل‌کاری برای تولیدات سینمایی، تلویزیونی یا صحنه‌ای. | تبلیغ تولیدات از راه‌هایی مانند مصاحبه درباره نمایش‌ها یا فیلم‌ها. | خواندن از روی فیلم‌نامه یا کتاب برای روایت کنش یا آگاهی‌بخشی و سرگرمی مخاطبان، با استفاده از لوازم صحنه اندک یا بدون آن. | خواندن یا رقصیدن در اجراهای نمایشی یا کمدی. | مطالعه و تمرین نقش از روی فیلم‌نامه برای تفسیر، یادگیری و از بر کردن دیالوگ‌ها، بدل‌کاری‌ها و نشانه‌های صحنه، مطابق دستور کارگردان. | لطیفه‌گویی، اجرای رقص و آواز و نمایش کوتاه کمدی، تقلید رفتار و صدای دیگران، تغییر حالت چهره و به‌کارگیری شگردهای دیگر برای سرگرم کردن تماشاگران. | همکاری نزدیک با کارگردانان، سایر بازیگران و نمایشنامه‌نویسان برای یافتن مناسب‌ترین تفسیر از نقش. | همکاری با سایر عوامل مسئول نور، لباس، گریم و لوازم صحنه. | نگارش متن اصیل یا اقتباسی برای نمایش‌های جدی، کمدی، عروسکی، روایت یا سایر اجراها.</t>
         </is>
       </c>
     </row>
